--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivanvlasov/code/kw/pereprava_bot/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\Telegram Desktop\27.06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1DD7CC-4794-904C-BB8B-B2B903611FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16560" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16560"/>
   </bookViews>
   <sheets>
     <sheet name="Переправы" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Название</t>
   </si>
@@ -91,9 +90,6 @@
     <t>На переправе {имя переправы} сегодня {число паромов} паромой</t>
   </si>
   <si>
-    <t>Вас приветствует официальный бот Переправы Салехард - Лабытнанги. Выберите необходимый пункт \"Меню\" или отправьте  команду /menu всли меню не отобразилось</t>
-  </si>
-  <si>
     <t>Стартовое сообщение пользователя</t>
   </si>
   <si>
@@ -131,12 +127,27 @@
   </si>
   <si>
     <t>appeal_message_success</t>
+  </si>
+  <si>
+    <t>Вас приветствует официальный бот Переправы Салехард - Лабытнанги. Выберите необходимый пункт \"Меню\" или отправьте  команду /menu если меню не отобразилось</t>
+  </si>
+  <si>
+    <t>Не трогать</t>
+  </si>
+  <si>
+    <t>Имя</t>
+  </si>
+  <si>
+    <t>Текст</t>
+  </si>
+  <si>
+    <t>Переправа 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -510,16 +521,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.875" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -535,39 +546,44 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="95.1640625" customWidth="1"/>
+    <col min="2" max="2" width="95.125" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,7 +592,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -585,7 +601,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -594,7 +610,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
     </row>
   </sheetData>
@@ -603,15 +619,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988BF993-BC4A-9249-BE1A-6A71B3CAF98C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.1640625" customWidth="1"/>
-    <col min="2" max="2" width="117.83203125" customWidth="1"/>
+    <col min="1" max="1" width="56.125" customWidth="1"/>
+    <col min="2" max="2" width="117.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -619,7 +635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -627,7 +643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -635,7 +651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -643,7 +659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -657,68 +673,79 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2200173E-5E00-5A4C-9D98-0B12B6FC3183}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="40.1640625" customWidth="1"/>
+    <col min="2" max="2" width="40.125" customWidth="1"/>
     <col min="3" max="3" width="158.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
